--- a/SKULA_Adnan_Mandzo_latest_fixed.xlsx
+++ b/SKULA_Adnan_Mandzo_latest_fixed.xlsx
@@ -1297,15 +1297,32 @@
     <col min="3" max="3" width="24.140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="20.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="34.42578125" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="9.140625" style="1"/>
+    <col min="7" max="16384" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25" ht="54" customHeight="1">
+      <c r="A1" s="60" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b/>
+              <sz val="8"/>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">qla.dev
+Braće Mulić 81, Sarajevo
+Bosnia</t>
+          </r>
+        </is>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBRAČUN TROŠKOVA SLUŽBENOG PUTOVANJA</t>
+        </is>
+      </c>
       <c r="D1" s="74"/>
       <c r="E1" s="74"/>
     </row>
@@ -1459,7 +1476,14 @@
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERVAUTO BELG-LUX S.A. TOTALENERGIES WAARLOOS ANTWERPEN</t>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">SERVAUTO BELG-LUX S.A. TOTALENERGIES WAARLOOS ANTWERPEN</t>
+          </r>
         </is>
       </c>
       <c r="C14" s="91">
@@ -1478,7 +1502,14 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEMEENTE ROTTERDAM</t>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">GEMEENTE ROTTERDAM</t>
+          </r>
         </is>
       </c>
       <c r="C15" s="91">
@@ -1497,7 +1528,14 @@
       </c>
       <c r="B16" s="93" t="inlineStr">
         <is>
-          <t xml:space="preserve">ART HOTEL ROTTERDAM</t>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">ART HOTEL ROTTERDAM</t>
+          </r>
         </is>
       </c>
       <c r="C16" s="91">
@@ -1516,7 +1554,14 @@
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEMEENTE ROTTERDAM</t>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">GEMEENTE ROTTERDAM</t>
+          </r>
         </is>
       </c>
       <c r="C17" s="91">
@@ -1563,7 +1608,14 @@
       </c>
       <c r="B20" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEMEENTE ROTTERDAM</t>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">GEMEENTE ROTTERDAM</t>
+          </r>
         </is>
       </c>
       <c r="C20" s="91">
@@ -1582,7 +1634,14 @@
       </c>
       <c r="B21" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHELL STAT. SANDELINGEN-OOST</t>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">SHELL STAT. SANDELINGEN-OOST</t>
+          </r>
         </is>
       </c>
       <c r="C21" s="91">
@@ -1601,7 +1660,14 @@
       </c>
       <c r="B22" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEMEENTE ROTTERDAM</t>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">GEMEENTE ROTTERDAM</t>
+          </r>
         </is>
       </c>
       <c r="C22" s="91">
@@ -1624,7 +1690,6 @@
       <c r="E23" s="90">
         <v>245.32</v>
       </c>
-      <c r="F23" s="20"/>
     </row>
     <row r="24" spans="1:6" s="3" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -1649,7 +1714,14 @@
       </c>
       <c r="B25" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOOKING.COM</t>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">BOOKING.COM</t>
+          </r>
         </is>
       </c>
       <c r="C25" s="91">
@@ -1668,7 +1740,14 @@
       </c>
       <c r="B26" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOTALENERGIES DAMPREMY</t>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">TOTALENERGIES DAMPREMY</t>
+          </r>
         </is>
       </c>
       <c r="C26" s="91">
@@ -1687,7 +1766,14 @@
       </c>
       <c r="B27" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">GATE BAR 21</t>
+          <r>
+            <rPr>
+              <sz val="9"/>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+            </rPr>
+            <t xml:space="preserve">GATE BAR 21</t>
+          </r>
         </is>
       </c>
       <c r="C27" s="91">
@@ -1867,8 +1953,9 @@
       <c r="A48" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A38:D38"/>
   </mergeCells>
